--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346506</v>
+        <v>121346907</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476187</v>
+        <v>476304</v>
       </c>
       <c r="R3" t="n">
-        <v>6874523</v>
+        <v>6874528</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346907</v>
+        <v>121345072</v>
       </c>
       <c r="B4" t="n">
-        <v>78335</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476304</v>
+        <v>476292</v>
       </c>
       <c r="R4" t="n">
-        <v>6874528</v>
+        <v>6874385</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345436</v>
+        <v>121347163</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R5" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347136</v>
+        <v>121346506</v>
       </c>
       <c r="B6" t="n">
-        <v>78334</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476285</v>
+        <v>476187</v>
       </c>
       <c r="R6" t="n">
-        <v>6874449</v>
+        <v>6874523</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344920</v>
+        <v>121347136</v>
       </c>
       <c r="B7" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476295</v>
+        <v>476285</v>
       </c>
       <c r="R7" t="n">
-        <v>6874425</v>
+        <v>6874449</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345072</v>
+        <v>121347158</v>
       </c>
       <c r="B8" t="n">
-        <v>78334</v>
+        <v>78338</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476292</v>
+        <v>476275</v>
       </c>
       <c r="R8" t="n">
-        <v>6874385</v>
+        <v>6874465</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1397,7 +1392,7 @@
         <v>121344997</v>
       </c>
       <c r="B9" t="n">
-        <v>78335</v>
+        <v>78338</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347163</v>
+        <v>121346600</v>
       </c>
       <c r="B10" t="n">
-        <v>78334</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476275</v>
+        <v>476180</v>
       </c>
       <c r="R10" t="n">
-        <v>6874465</v>
+        <v>6874547</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1572,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346600</v>
+        <v>121344920</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>78337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476180</v>
+        <v>476295</v>
       </c>
       <c r="R11" t="n">
-        <v>6874547</v>
+        <v>6874425</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347158</v>
+        <v>121345436</v>
       </c>
       <c r="B12" t="n">
-        <v>78335</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476275</v>
+        <v>476155</v>
       </c>
       <c r="R12" t="n">
-        <v>6874465</v>
+        <v>6874449</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379273</v>
+        <v>121380965</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476190</v>
+        <v>476301</v>
       </c>
       <c r="R13" t="n">
-        <v>6874450</v>
+        <v>6874406</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121380965</v>
+        <v>121379273</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476301</v>
+        <v>476190</v>
       </c>
       <c r="R14" t="n">
-        <v>6874406</v>
+        <v>6874450</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1990,6 +1985,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,7 +2019,7 @@
         <v>121379884</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346600</v>
+        <v>121344920</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>78337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476180</v>
+        <v>476295</v>
       </c>
       <c r="R10" t="n">
-        <v>6874547</v>
+        <v>6874425</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121344920</v>
+        <v>121346600</v>
       </c>
       <c r="B11" t="n">
-        <v>78337</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476295</v>
+        <v>476180</v>
       </c>
       <c r="R11" t="n">
-        <v>6874425</v>
+        <v>6874547</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121344920</v>
+        <v>121346600</v>
       </c>
       <c r="B10" t="n">
-        <v>78337</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476295</v>
+        <v>476180</v>
       </c>
       <c r="R10" t="n">
-        <v>6874425</v>
+        <v>6874547</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346600</v>
+        <v>121344920</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>78337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476180</v>
+        <v>476295</v>
       </c>
       <c r="R11" t="n">
-        <v>6874547</v>
+        <v>6874425</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346907</v>
+        <v>121347158</v>
       </c>
       <c r="B3" t="n">
         <v>78338</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476304</v>
+        <v>476275</v>
       </c>
       <c r="R3" t="n">
-        <v>6874528</v>
+        <v>6874465</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345072</v>
+        <v>121346907</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>78338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476292</v>
+        <v>476304</v>
       </c>
       <c r="R4" t="n">
-        <v>6874385</v>
+        <v>6874528</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347163</v>
+        <v>121346600</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476275</v>
+        <v>476180</v>
       </c>
       <c r="R5" t="n">
-        <v>6874465</v>
+        <v>6874547</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346506</v>
+        <v>121347163</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78337</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476187</v>
+        <v>476275</v>
       </c>
       <c r="R6" t="n">
-        <v>6874523</v>
+        <v>6874465</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347136</v>
+        <v>121345072</v>
       </c>
       <c r="B7" t="n">
         <v>78337</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476285</v>
+        <v>476292</v>
       </c>
       <c r="R7" t="n">
-        <v>6874449</v>
+        <v>6874385</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347158</v>
+        <v>121344997</v>
       </c>
       <c r="B8" t="n">
         <v>78338</v>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476275</v>
+        <v>476295</v>
       </c>
       <c r="R8" t="n">
-        <v>6874465</v>
+        <v>6874425</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121344997</v>
+        <v>121345436</v>
       </c>
       <c r="B9" t="n">
-        <v>78338</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476295</v>
+        <v>476155</v>
       </c>
       <c r="R9" t="n">
-        <v>6874425</v>
+        <v>6874449</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346600</v>
+        <v>121346506</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476180</v>
+        <v>476187</v>
       </c>
       <c r="R10" t="n">
-        <v>6874547</v>
+        <v>6874523</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345436</v>
+        <v>121347136</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>78337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,7 +1745,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476155</v>
+        <v>476285</v>
       </c>
       <c r="R12" t="n">
         <v>6874449</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347158</v>
+        <v>121346506</v>
       </c>
       <c r="B3" t="n">
-        <v>78338</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476275</v>
+        <v>476187</v>
       </c>
       <c r="R3" t="n">
-        <v>6874465</v>
+        <v>6874523</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346907</v>
+        <v>121347163</v>
       </c>
       <c r="B4" t="n">
-        <v>78338</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476304</v>
+        <v>476275</v>
       </c>
       <c r="R4" t="n">
-        <v>6874528</v>
+        <v>6874465</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346600</v>
+        <v>121347136</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476180</v>
+        <v>476285</v>
       </c>
       <c r="R5" t="n">
-        <v>6874547</v>
+        <v>6874449</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347163</v>
+        <v>121346600</v>
       </c>
       <c r="B6" t="n">
-        <v>78337</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476275</v>
+        <v>476180</v>
       </c>
       <c r="R6" t="n">
-        <v>6874465</v>
+        <v>6874547</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,7 @@
         <v>121345072</v>
       </c>
       <c r="B7" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>121344997</v>
       </c>
       <c r="B8" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345436</v>
+        <v>121347158</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>78341</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R9" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346506</v>
+        <v>121346907</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78341</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476187</v>
+        <v>476304</v>
       </c>
       <c r="R10" t="n">
-        <v>6874523</v>
+        <v>6874528</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1606,7 +1601,7 @@
         <v>121344920</v>
       </c>
       <c r="B11" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347136</v>
+        <v>121345436</v>
       </c>
       <c r="B12" t="n">
-        <v>78337</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,7 +1740,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476285</v>
+        <v>476155</v>
       </c>
       <c r="R12" t="n">
         <v>6874449</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,7 +1810,7 @@
         <v>121380965</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>121379884</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346506</v>
+        <v>121347136</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476187</v>
+        <v>476285</v>
       </c>
       <c r="R3" t="n">
-        <v>6874523</v>
+        <v>6874449</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347163</v>
+        <v>121344997</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476275</v>
+        <v>476295</v>
       </c>
       <c r="R4" t="n">
-        <v>6874465</v>
+        <v>6874425</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347136</v>
+        <v>121345436</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476285</v>
+        <v>476155</v>
       </c>
       <c r="R5" t="n">
         <v>6874449</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346600</v>
+        <v>121344920</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>78340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476180</v>
+        <v>476295</v>
       </c>
       <c r="R6" t="n">
-        <v>6874547</v>
+        <v>6874425</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345072</v>
+        <v>121346506</v>
       </c>
       <c r="B7" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476292</v>
+        <v>476187</v>
       </c>
       <c r="R7" t="n">
-        <v>6874385</v>
+        <v>6874523</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121344997</v>
+        <v>121346600</v>
       </c>
       <c r="B8" t="n">
-        <v>78341</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476295</v>
+        <v>476180</v>
       </c>
       <c r="R8" t="n">
-        <v>6874425</v>
+        <v>6874547</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1368,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347158</v>
+        <v>121346907</v>
       </c>
       <c r="B9" t="n">
         <v>78341</v>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476275</v>
+        <v>476304</v>
       </c>
       <c r="R9" t="n">
-        <v>6874465</v>
+        <v>6874528</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346907</v>
+        <v>121347158</v>
       </c>
       <c r="B10" t="n">
         <v>78341</v>
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476304</v>
+        <v>476275</v>
       </c>
       <c r="R10" t="n">
-        <v>6874528</v>
+        <v>6874465</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121344920</v>
+        <v>121345072</v>
       </c>
       <c r="B11" t="n">
         <v>78340</v>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476295</v>
+        <v>476292</v>
       </c>
       <c r="R11" t="n">
-        <v>6874425</v>
+        <v>6874385</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345436</v>
+        <v>121347163</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>78340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R12" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121380965</v>
+        <v>121379273</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476301</v>
+        <v>476190</v>
       </c>
       <c r="R13" t="n">
-        <v>6874406</v>
+        <v>6874450</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379273</v>
+        <v>121380965</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476190</v>
+        <v>476301</v>
       </c>
       <c r="R14" t="n">
-        <v>6874450</v>
+        <v>6874406</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1985,11 +1990,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347136</v>
+        <v>121344997</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476285</v>
+        <v>476295</v>
       </c>
       <c r="R3" t="n">
-        <v>6874449</v>
+        <v>6874425</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344997</v>
+        <v>121345072</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476295</v>
+        <v>476292</v>
       </c>
       <c r="R4" t="n">
-        <v>6874425</v>
+        <v>6874385</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345436</v>
+        <v>121344920</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>78343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476155</v>
+        <v>476295</v>
       </c>
       <c r="R5" t="n">
-        <v>6874449</v>
+        <v>6874425</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344920</v>
+        <v>121346600</v>
       </c>
       <c r="B6" t="n">
-        <v>78340</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476295</v>
+        <v>476180</v>
       </c>
       <c r="R6" t="n">
-        <v>6874425</v>
+        <v>6874547</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346506</v>
+        <v>121347136</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476187</v>
+        <v>476285</v>
       </c>
       <c r="R7" t="n">
-        <v>6874523</v>
+        <v>6874449</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346600</v>
+        <v>121347163</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>78343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476180</v>
+        <v>476275</v>
       </c>
       <c r="R8" t="n">
-        <v>6874547</v>
+        <v>6874465</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346907</v>
+        <v>121345436</v>
       </c>
       <c r="B9" t="n">
-        <v>78341</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476304</v>
+        <v>476155</v>
       </c>
       <c r="R9" t="n">
-        <v>6874528</v>
+        <v>6874449</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1475,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347158</v>
+        <v>121346506</v>
       </c>
       <c r="B10" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476275</v>
+        <v>476187</v>
       </c>
       <c r="R10" t="n">
-        <v>6874465</v>
+        <v>6874523</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345072</v>
+        <v>121346907</v>
       </c>
       <c r="B11" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476292</v>
+        <v>476304</v>
       </c>
       <c r="R11" t="n">
-        <v>6874385</v>
+        <v>6874528</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347163</v>
+        <v>121347158</v>
       </c>
       <c r="B12" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379273</v>
+        <v>121380965</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476190</v>
+        <v>476301</v>
       </c>
       <c r="R13" t="n">
-        <v>6874450</v>
+        <v>6874406</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121380965</v>
+        <v>121379884</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476301</v>
+        <v>476215</v>
       </c>
       <c r="R14" t="n">
-        <v>6874406</v>
+        <v>6874504</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121379884</v>
+        <v>121379273</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476215</v>
+        <v>476190</v>
       </c>
       <c r="R15" t="n">
-        <v>6874504</v>
+        <v>6874450</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2092,6 +2087,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121344997</v>
+        <v>121347136</v>
       </c>
       <c r="B3" t="n">
-        <v>78344</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476295</v>
+        <v>476285</v>
       </c>
       <c r="R3" t="n">
-        <v>6874425</v>
+        <v>6874449</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345072</v>
+        <v>121344920</v>
       </c>
       <c r="B4" t="n">
         <v>78343</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476292</v>
+        <v>476295</v>
       </c>
       <c r="R4" t="n">
-        <v>6874385</v>
+        <v>6874425</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344920</v>
+        <v>121346907</v>
       </c>
       <c r="B5" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476295</v>
+        <v>476304</v>
       </c>
       <c r="R5" t="n">
-        <v>6874425</v>
+        <v>6874528</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346600</v>
+        <v>121345072</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>78343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476180</v>
+        <v>476292</v>
       </c>
       <c r="R6" t="n">
-        <v>6874547</v>
+        <v>6874385</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347136</v>
+        <v>121345436</v>
       </c>
       <c r="B7" t="n">
-        <v>78343</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476285</v>
+        <v>476155</v>
       </c>
       <c r="R7" t="n">
         <v>6874449</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347163</v>
+        <v>121347158</v>
       </c>
       <c r="B8" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345436</v>
+        <v>121347163</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>78343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R9" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346506</v>
+        <v>121346600</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476187</v>
+        <v>476180</v>
       </c>
       <c r="R10" t="n">
-        <v>6874523</v>
+        <v>6874547</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1577,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346907</v>
+        <v>121344997</v>
       </c>
       <c r="B11" t="n">
         <v>78344</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476304</v>
+        <v>476295</v>
       </c>
       <c r="R11" t="n">
-        <v>6874528</v>
+        <v>6874425</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347158</v>
+        <v>121346506</v>
       </c>
       <c r="B12" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476275</v>
+        <v>476187</v>
       </c>
       <c r="R12" t="n">
-        <v>6874465</v>
+        <v>6874523</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379884</v>
+        <v>121379273</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476215</v>
+        <v>476190</v>
       </c>
       <c r="R14" t="n">
-        <v>6874504</v>
+        <v>6874450</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1985,6 +1985,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121379273</v>
+        <v>121379884</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476190</v>
+        <v>476215</v>
       </c>
       <c r="R15" t="n">
-        <v>6874450</v>
+        <v>6874504</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2087,11 +2092,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347136</v>
+        <v>121345436</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476285</v>
+        <v>476155</v>
       </c>
       <c r="R3" t="n">
         <v>6874449</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344920</v>
+        <v>121346506</v>
       </c>
       <c r="B4" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476295</v>
+        <v>476187</v>
       </c>
       <c r="R4" t="n">
-        <v>6874425</v>
+        <v>6874523</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346907</v>
+        <v>121344920</v>
       </c>
       <c r="B5" t="n">
         <v>78344</v>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476304</v>
+        <v>476295</v>
       </c>
       <c r="R5" t="n">
-        <v>6874528</v>
+        <v>6874425</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1091,7 @@
         <v>121345072</v>
       </c>
       <c r="B6" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345436</v>
+        <v>121347136</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>78344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,7 +1230,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476155</v>
+        <v>476285</v>
       </c>
       <c r="R7" t="n">
         <v>6874449</v>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347158</v>
+        <v>121344997</v>
       </c>
       <c r="B8" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476275</v>
+        <v>476295</v>
       </c>
       <c r="R8" t="n">
-        <v>6874465</v>
+        <v>6874425</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347163</v>
+        <v>121347158</v>
       </c>
       <c r="B9" t="n">
-        <v>78343</v>
+        <v>78345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346600</v>
+        <v>121346907</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>78345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476180</v>
+        <v>476304</v>
       </c>
       <c r="R10" t="n">
-        <v>6874547</v>
+        <v>6874528</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1572,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121344997</v>
+        <v>121347163</v>
       </c>
       <c r="B11" t="n">
         <v>78344</v>
@@ -1619,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476295</v>
+        <v>476275</v>
       </c>
       <c r="R11" t="n">
-        <v>6874425</v>
+        <v>6874465</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346506</v>
+        <v>121346600</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476187</v>
+        <v>476180</v>
       </c>
       <c r="R12" t="n">
-        <v>6874523</v>
+        <v>6874547</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121380965</v>
+        <v>121379273</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476301</v>
+        <v>476190</v>
       </c>
       <c r="R13" t="n">
-        <v>6874406</v>
+        <v>6874450</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379273</v>
+        <v>121379884</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476190</v>
+        <v>476215</v>
       </c>
       <c r="R14" t="n">
-        <v>6874450</v>
+        <v>6874504</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1985,11 +1990,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121379884</v>
+        <v>121380965</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476215</v>
+        <v>476301</v>
       </c>
       <c r="R15" t="n">
-        <v>6874504</v>
+        <v>6874406</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345436</v>
+        <v>121346907</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>78346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476155</v>
+        <v>476304</v>
       </c>
       <c r="R3" t="n">
-        <v>6874449</v>
+        <v>6874528</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346506</v>
+        <v>121347158</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476187</v>
+        <v>476275</v>
       </c>
       <c r="R4" t="n">
-        <v>6874523</v>
+        <v>6874465</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344920</v>
+        <v>121346600</v>
       </c>
       <c r="B5" t="n">
-        <v>78344</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476295</v>
+        <v>476180</v>
       </c>
       <c r="R5" t="n">
-        <v>6874425</v>
+        <v>6874547</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345072</v>
+        <v>121347163</v>
       </c>
       <c r="B6" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476292</v>
+        <v>476275</v>
       </c>
       <c r="R6" t="n">
-        <v>6874385</v>
+        <v>6874465</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1193,7 +1193,7 @@
         <v>121347136</v>
       </c>
       <c r="B7" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121344997</v>
+        <v>121344920</v>
       </c>
       <c r="B8" t="n">
         <v>78345</v>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347158</v>
+        <v>121345072</v>
       </c>
       <c r="B9" t="n">
         <v>78345</v>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476275</v>
+        <v>476292</v>
       </c>
       <c r="R9" t="n">
-        <v>6874465</v>
+        <v>6874385</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346907</v>
+        <v>121346506</v>
       </c>
       <c r="B10" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476304</v>
+        <v>476187</v>
       </c>
       <c r="R10" t="n">
-        <v>6874528</v>
+        <v>6874523</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347163</v>
+        <v>121345436</v>
       </c>
       <c r="B11" t="n">
-        <v>78344</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476275</v>
+        <v>476155</v>
       </c>
       <c r="R11" t="n">
-        <v>6874465</v>
+        <v>6874449</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,6 +1674,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346600</v>
+        <v>121344997</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>78346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476180</v>
+        <v>476295</v>
       </c>
       <c r="R12" t="n">
-        <v>6874547</v>
+        <v>6874425</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,7 +1810,7 @@
         <v>121379273</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>121379884</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>121380965</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346907</v>
+        <v>121347163</v>
       </c>
       <c r="B3" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476304</v>
+        <v>476275</v>
       </c>
       <c r="R3" t="n">
-        <v>6874528</v>
+        <v>6874465</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347158</v>
+        <v>121346506</v>
       </c>
       <c r="B4" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476275</v>
+        <v>476187</v>
       </c>
       <c r="R4" t="n">
-        <v>6874465</v>
+        <v>6874523</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346600</v>
+        <v>121347158</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>78346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476180</v>
+        <v>476275</v>
       </c>
       <c r="R5" t="n">
-        <v>6874547</v>
+        <v>6874465</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347163</v>
+        <v>121347136</v>
       </c>
       <c r="B6" t="n">
         <v>78345</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476275</v>
+        <v>476285</v>
       </c>
       <c r="R6" t="n">
-        <v>6874465</v>
+        <v>6874449</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347136</v>
+        <v>121344920</v>
       </c>
       <c r="B7" t="n">
         <v>78345</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476285</v>
+        <v>476295</v>
       </c>
       <c r="R7" t="n">
-        <v>6874449</v>
+        <v>6874425</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121344920</v>
+        <v>121345436</v>
       </c>
       <c r="B8" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476295</v>
+        <v>476155</v>
       </c>
       <c r="R8" t="n">
-        <v>6874425</v>
+        <v>6874449</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346506</v>
+        <v>121344997</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476187</v>
+        <v>476295</v>
       </c>
       <c r="R10" t="n">
-        <v>6874523</v>
+        <v>6874425</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345436</v>
+        <v>121346600</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476155</v>
+        <v>476180</v>
       </c>
       <c r="R11" t="n">
-        <v>6874449</v>
+        <v>6874547</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121344997</v>
+        <v>121346907</v>
       </c>
       <c r="B12" t="n">
         <v>78346</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476295</v>
+        <v>476304</v>
       </c>
       <c r="R12" t="n">
-        <v>6874425</v>
+        <v>6874528</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379273</v>
+        <v>121379884</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476190</v>
+        <v>476215</v>
       </c>
       <c r="R13" t="n">
-        <v>6874450</v>
+        <v>6874504</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379884</v>
+        <v>121379273</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476215</v>
+        <v>476190</v>
       </c>
       <c r="R14" t="n">
-        <v>6874504</v>
+        <v>6874450</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1990,6 +1985,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347163</v>
+        <v>121347158</v>
       </c>
       <c r="B3" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346506</v>
+        <v>121345072</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476187</v>
+        <v>476292</v>
       </c>
       <c r="R4" t="n">
-        <v>6874523</v>
+        <v>6874385</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347158</v>
+        <v>121346907</v>
       </c>
       <c r="B5" t="n">
         <v>78346</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476275</v>
+        <v>476304</v>
       </c>
       <c r="R5" t="n">
-        <v>6874465</v>
+        <v>6874528</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345436</v>
+        <v>121346600</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476155</v>
+        <v>476180</v>
       </c>
       <c r="R8" t="n">
-        <v>6874449</v>
+        <v>6874547</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345072</v>
+        <v>121345436</v>
       </c>
       <c r="B9" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476292</v>
+        <v>476155</v>
       </c>
       <c r="R9" t="n">
-        <v>6874385</v>
+        <v>6874449</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1470,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346600</v>
+        <v>121346506</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476180</v>
+        <v>476187</v>
       </c>
       <c r="R11" t="n">
-        <v>6874547</v>
+        <v>6874523</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346907</v>
+        <v>121347163</v>
       </c>
       <c r="B12" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476304</v>
+        <v>476275</v>
       </c>
       <c r="R12" t="n">
-        <v>6874528</v>
+        <v>6874465</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379884</v>
+        <v>121379273</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476215</v>
+        <v>476190</v>
       </c>
       <c r="R13" t="n">
-        <v>6874504</v>
+        <v>6874450</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379273</v>
+        <v>121379884</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476190</v>
+        <v>476215</v>
       </c>
       <c r="R14" t="n">
-        <v>6874450</v>
+        <v>6874504</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1985,11 +1990,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347158</v>
+        <v>121346907</v>
       </c>
       <c r="B3" t="n">
         <v>78346</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476275</v>
+        <v>476304</v>
       </c>
       <c r="R3" t="n">
-        <v>6874465</v>
+        <v>6874528</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345072</v>
+        <v>121344997</v>
       </c>
       <c r="B4" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476292</v>
+        <v>476295</v>
       </c>
       <c r="R4" t="n">
-        <v>6874385</v>
+        <v>6874425</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346907</v>
+        <v>121346506</v>
       </c>
       <c r="B5" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476304</v>
+        <v>476187</v>
       </c>
       <c r="R5" t="n">
-        <v>6874528</v>
+        <v>6874523</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344920</v>
+        <v>121345072</v>
       </c>
       <c r="B7" t="n">
         <v>78345</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476295</v>
+        <v>476292</v>
       </c>
       <c r="R7" t="n">
-        <v>6874425</v>
+        <v>6874385</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346600</v>
+        <v>121347163</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>78345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476180</v>
+        <v>476275</v>
       </c>
       <c r="R8" t="n">
-        <v>6874547</v>
+        <v>6874465</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1363,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345436</v>
+        <v>121347158</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78346</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R9" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1470,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121344997</v>
+        <v>121345436</v>
       </c>
       <c r="B10" t="n">
-        <v>78346</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476295</v>
+        <v>476155</v>
       </c>
       <c r="R10" t="n">
-        <v>6874425</v>
+        <v>6874449</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1577,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346506</v>
+        <v>121344920</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476187</v>
+        <v>476295</v>
       </c>
       <c r="R11" t="n">
-        <v>6874523</v>
+        <v>6874425</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347163</v>
+        <v>121346600</v>
       </c>
       <c r="B12" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476275</v>
+        <v>476180</v>
       </c>
       <c r="R12" t="n">
-        <v>6874465</v>
+        <v>6874547</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347158</v>
+        <v>121345436</v>
       </c>
       <c r="B9" t="n">
-        <v>78346</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476275</v>
+        <v>476155</v>
       </c>
       <c r="R9" t="n">
-        <v>6874465</v>
+        <v>6874449</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345436</v>
+        <v>121347158</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R10" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345436</v>
+        <v>121347158</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78346</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476155</v>
+        <v>476275</v>
       </c>
       <c r="R9" t="n">
-        <v>6874449</v>
+        <v>6874465</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347158</v>
+        <v>121345436</v>
       </c>
       <c r="B10" t="n">
-        <v>78346</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476275</v>
+        <v>476155</v>
       </c>
       <c r="R10" t="n">
-        <v>6874465</v>
+        <v>6874449</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1572,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran. Fuktskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346907</v>
+        <v>121344920</v>
       </c>
       <c r="B3" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476304</v>
+        <v>476295</v>
       </c>
       <c r="R3" t="n">
-        <v>6874528</v>
+        <v>6874425</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344997</v>
+        <v>121347163</v>
       </c>
       <c r="B4" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476295</v>
+        <v>476275</v>
       </c>
       <c r="R4" t="n">
-        <v>6874425</v>
+        <v>6874465</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346506</v>
+        <v>121346600</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476187</v>
+        <v>476180</v>
       </c>
       <c r="R5" t="n">
-        <v>6874523</v>
+        <v>6874547</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347136</v>
+        <v>121346907</v>
       </c>
       <c r="B6" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476285</v>
+        <v>476304</v>
       </c>
       <c r="R6" t="n">
-        <v>6874449</v>
+        <v>6874528</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345072</v>
+        <v>121346506</v>
       </c>
       <c r="B7" t="n">
-        <v>78345</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476292</v>
+        <v>476187</v>
       </c>
       <c r="R7" t="n">
-        <v>6874385</v>
+        <v>6874523</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347163</v>
+        <v>121347136</v>
       </c>
       <c r="B8" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476275</v>
+        <v>476285</v>
       </c>
       <c r="R8" t="n">
-        <v>6874465</v>
+        <v>6874449</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1392,7 +1397,7 @@
         <v>121347158</v>
       </c>
       <c r="B9" t="n">
-        <v>78346</v>
+        <v>78353</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,7 +1499,7 @@
         <v>121345436</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121344920</v>
+        <v>121345072</v>
       </c>
       <c r="B11" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476295</v>
+        <v>476292</v>
       </c>
       <c r="R11" t="n">
-        <v>6874425</v>
+        <v>6874385</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346600</v>
+        <v>121344997</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476180</v>
+        <v>476295</v>
       </c>
       <c r="R12" t="n">
-        <v>6874547</v>
+        <v>6874425</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379273</v>
+        <v>121379884</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476190</v>
+        <v>476215</v>
       </c>
       <c r="R13" t="n">
-        <v>6874450</v>
+        <v>6874504</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379884</v>
+        <v>121380965</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476215</v>
+        <v>476301</v>
       </c>
       <c r="R14" t="n">
-        <v>6874504</v>
+        <v>6874406</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121380965</v>
+        <v>121379273</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476301</v>
+        <v>476190</v>
       </c>
       <c r="R15" t="n">
-        <v>6874406</v>
+        <v>6874450</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2092,6 +2087,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall 5-7 meter upp.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124128318</v>
+        <v>124129480</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,47 +2130,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476249</v>
+        <v>476167</v>
       </c>
       <c r="R16" t="n">
-        <v>6874403</v>
+        <v>6874510</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2229,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124129480</v>
+        <v>124128318</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,38 +2232,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476167</v>
+        <v>476249</v>
       </c>
       <c r="R17" t="n">
-        <v>6874510</v>
+        <v>6874403</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124129672</v>
+        <v>124127903</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,41 +2343,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476186</v>
+        <v>476266</v>
       </c>
       <c r="R18" t="n">
-        <v>6874546</v>
+        <v>6874348</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2433,7 +2442,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124127903</v>
+        <v>124127703</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2468,7 +2477,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2482,13 +2491,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476266</v>
+        <v>476284</v>
       </c>
       <c r="R19" t="n">
-        <v>6874348</v>
+        <v>6874333</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124127703</v>
+        <v>124129672</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,47 +2565,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476284</v>
+        <v>476186</v>
       </c>
       <c r="R20" t="n">
-        <v>6874333</v>
+        <v>6874546</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124129480</v>
+        <v>124127703</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,38 +2130,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476167</v>
+        <v>476284</v>
       </c>
       <c r="R16" t="n">
-        <v>6874510</v>
+        <v>6874333</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2331,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124127903</v>
+        <v>124129480</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,50 +2352,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476266</v>
+        <v>476167</v>
       </c>
       <c r="R18" t="n">
-        <v>6874348</v>
+        <v>6874510</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124127703</v>
+        <v>124127903</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476284</v>
+        <v>476266</v>
       </c>
       <c r="R19" t="n">
-        <v>6874333</v>
+        <v>6874348</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2229,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124128318</v>
+        <v>124129480</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,47 +2241,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476249</v>
+        <v>476167</v>
       </c>
       <c r="R17" t="n">
-        <v>6874403</v>
+        <v>6874510</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2340,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124129480</v>
+        <v>124128318</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,38 +2343,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476167</v>
+        <v>476249</v>
       </c>
       <c r="R18" t="n">
-        <v>6874510</v>
+        <v>6874403</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124127903</v>
+        <v>124129672</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,50 +2454,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476266</v>
+        <v>476186</v>
       </c>
       <c r="R19" t="n">
-        <v>6874348</v>
+        <v>6874546</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2553,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124129672</v>
+        <v>124127903</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,41 +2556,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476186</v>
+        <v>476266</v>
       </c>
       <c r="R20" t="n">
-        <v>6874546</v>
+        <v>6874348</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124127703</v>
+        <v>124129480</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,47 +2130,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476284</v>
+        <v>476167</v>
       </c>
       <c r="R16" t="n">
-        <v>6874333</v>
+        <v>6874510</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2229,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124129480</v>
+        <v>124127703</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,38 +2232,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476167</v>
+        <v>476284</v>
       </c>
       <c r="R17" t="n">
-        <v>6874510</v>
+        <v>6874333</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124128318</v>
+        <v>124129672</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,47 +2343,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476249</v>
+        <v>476186</v>
       </c>
       <c r="R18" t="n">
-        <v>6874403</v>
+        <v>6874546</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2442,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124129672</v>
+        <v>124127903</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,41 +2445,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476186</v>
+        <v>476266</v>
       </c>
       <c r="R19" t="n">
-        <v>6874546</v>
+        <v>6874348</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124127903</v>
+        <v>124128318</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476266</v>
+        <v>476249</v>
       </c>
       <c r="R20" t="n">
-        <v>6874348</v>
+        <v>6874403</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124127703</v>
+        <v>124129672</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,47 +2232,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476284</v>
+        <v>476186</v>
       </c>
       <c r="R17" t="n">
-        <v>6874333</v>
+        <v>6874546</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2331,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124129672</v>
+        <v>124127703</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,38 +2334,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476186</v>
+        <v>476284</v>
       </c>
       <c r="R18" t="n">
-        <v>6874546</v>
+        <v>6874333</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124127903</v>
+        <v>124128318</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476266</v>
+        <v>476249</v>
       </c>
       <c r="R19" t="n">
-        <v>6874348</v>
+        <v>6874403</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124128318</v>
+        <v>124127903</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476249</v>
+        <v>476266</v>
       </c>
       <c r="R20" t="n">
-        <v>6874403</v>
+        <v>6874348</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124129672</v>
+        <v>124127703</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2232,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476186</v>
+        <v>476284</v>
       </c>
       <c r="R17" t="n">
-        <v>6874546</v>
+        <v>6874333</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2322,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124127703</v>
+        <v>124129672</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,47 +2343,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476284</v>
+        <v>476186</v>
       </c>
       <c r="R18" t="n">
-        <v>6874333</v>
+        <v>6874546</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124127703</v>
+        <v>124129672</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,47 +2232,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476284</v>
+        <v>476186</v>
       </c>
       <c r="R17" t="n">
-        <v>6874333</v>
+        <v>6874546</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2331,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124129672</v>
+        <v>124127703</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,38 +2334,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476186</v>
+        <v>476284</v>
       </c>
       <c r="R18" t="n">
-        <v>6874546</v>
+        <v>6874333</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124129480</v>
+        <v>124127903</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,41 +2130,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476167</v>
+        <v>476266</v>
       </c>
       <c r="R16" t="n">
-        <v>6874510</v>
+        <v>6874348</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124129672</v>
+        <v>124127703</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2241,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476186</v>
+        <v>476284</v>
       </c>
       <c r="R17" t="n">
-        <v>6874546</v>
+        <v>6874333</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2322,7 +2340,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124127703</v>
+        <v>124128318</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2371,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476284</v>
+        <v>476249</v>
       </c>
       <c r="R18" t="n">
-        <v>6874333</v>
+        <v>6874403</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2433,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124128318</v>
+        <v>124129480</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,47 +2463,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476249</v>
+        <v>476167</v>
       </c>
       <c r="R19" t="n">
-        <v>6874403</v>
+        <v>6874510</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124127903</v>
+        <v>124129672</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,50 +2565,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476266</v>
+        <v>476186</v>
       </c>
       <c r="R20" t="n">
-        <v>6874348</v>
+        <v>6874546</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124127903</v>
+        <v>124127703</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476266</v>
+        <v>476284</v>
       </c>
       <c r="R16" t="n">
-        <v>6874348</v>
+        <v>6874333</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124127703</v>
+        <v>124128318</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476284</v>
+        <v>476249</v>
       </c>
       <c r="R17" t="n">
-        <v>6874333</v>
+        <v>6874403</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124128318</v>
+        <v>124129480</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,47 +2352,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476249</v>
+        <v>476167</v>
       </c>
       <c r="R18" t="n">
-        <v>6874403</v>
+        <v>6874510</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2451,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124129480</v>
+        <v>124129672</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,21 +2458,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476167</v>
+        <v>476186</v>
       </c>
       <c r="R19" t="n">
-        <v>6874510</v>
+        <v>6874546</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2553,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124129672</v>
+        <v>124127903</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,41 +2556,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476186</v>
+        <v>476266</v>
       </c>
       <c r="R20" t="n">
-        <v>6874546</v>
+        <v>6874348</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2024 artfynd.xlsx
+++ b/artfynd/A 54196-2024 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124127703</v>
+        <v>124129672</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,47 +2130,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476284</v>
+        <v>476186</v>
       </c>
       <c r="R16" t="n">
-        <v>6874333</v>
+        <v>6874546</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2229,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124128318</v>
+        <v>124127703</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2278,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476249</v>
+        <v>476284</v>
       </c>
       <c r="R17" t="n">
-        <v>6874403</v>
+        <v>6874333</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2442,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124129672</v>
+        <v>124127903</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,41 +2445,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rengsjöbergen, Rengsjöbergen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476186</v>
+        <v>476266</v>
       </c>
       <c r="R19" t="n">
-        <v>6874546</v>
+        <v>6874348</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124127903</v>
+        <v>124128318</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476266</v>
+        <v>476249</v>
       </c>
       <c r="R20" t="n">
-        <v>6874348</v>
+        <v>6874403</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
